--- a/Azure_Remediation_ReportBT.xlsx
+++ b/Azure_Remediation_ReportBT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\JobLPst\CSVFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{834770B1-3AF7-439E-A178-D9EDCD05FC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04225FD3-19F1-480E-9E4D-DF924AE276E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC389A00-2338-406C-9DA3-8C4D893FA687}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Command Tier</t>
   </si>
   <si>
-    <t>Federal Agency / Branch</t>
-  </si>
-  <si>
     <t>Total Active Units</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Nissan Motor Co</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,7 @@
   <autoFilter ref="A1:E13" xr:uid="{A76D111D-A0CB-4B70-9402-B527F954132E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A6EA78D1-E642-4DCE-84A0-93D22FE84B02}" name="Command Tier"/>
-    <tableColumn id="2" xr3:uid="{B89B13A9-1213-47CC-BB86-97FAFCD067D6}" name="Federal Agency / Branch"/>
+    <tableColumn id="2" xr3:uid="{B89B13A9-1213-47CC-BB86-97FAFCD067D6}" name="Agency"/>
     <tableColumn id="3" xr3:uid="{053CEAB0-4428-462B-81E1-34EFDD684996}" name="Total Active Units"/>
     <tableColumn id="4" xr3:uid="{C3CFEA51-9597-4FD8-A937-AB3204277EF8}" name="Precise Unit Cost (MSRP)" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{F2B1958A-1318-428E-92EC-348CFE62803D}" name="Total Financial Footprint" dataDxfId="0"/>
@@ -985,24 +985,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
       </c>
       <c r="C2">
         <v>36448246</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
       </c>
       <c r="C3">
         <v>32971705</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
       </c>
       <c r="C4">
         <v>32751775</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>32063260</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>32443716</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>31822170</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
       <c r="C8">
         <v>32880396</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>31853081</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>31460870</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>32202276</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12">
         <v>31532498</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>29925570</v>

--- a/Azure_Remediation_ReportBT.xlsx
+++ b/Azure_Remediation_ReportBT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04225FD3-19F1-480E-9E4D-DF924AE276E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C2BF9-55E2-4071-8C0D-1522FD0EC5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC389A00-2338-406C-9DA3-8C4D893FA687}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
-    <t>Command Tier</t>
-  </si>
-  <si>
     <t>Total Active Units</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Agency</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A76D111D-A0CB-4B70-9402-B527F954132E}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0">
   <autoFilter ref="A1:E13" xr:uid="{A76D111D-A0CB-4B70-9402-B527F954132E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A6EA78D1-E642-4DCE-84A0-93D22FE84B02}" name="Command Tier"/>
+    <tableColumn id="1" xr3:uid="{A6EA78D1-E642-4DCE-84A0-93D22FE84B02}" name="Region"/>
     <tableColumn id="2" xr3:uid="{B89B13A9-1213-47CC-BB86-97FAFCD067D6}" name="Agency"/>
     <tableColumn id="3" xr3:uid="{053CEAB0-4428-462B-81E1-34EFDD684996}" name="Total Active Units"/>
     <tableColumn id="4" xr3:uid="{C3CFEA51-9597-4FD8-A937-AB3204277EF8}" name="Precise Unit Cost (MSRP)" dataDxfId="1"/>
@@ -982,27 +982,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>36448246</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
       </c>
       <c r="C3">
         <v>32971705</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4">
         <v>32751775</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>32063260</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>32443716</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>31822170</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
       </c>
       <c r="C8">
         <v>32880396</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>31853081</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>31460870</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>32202276</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>31532498</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>29925570</v>
